--- a/utilities/genetic_diversity/genetic_diversity_r/RSV_diversity_results_final.xlsx
+++ b/utilities/genetic_diversity/genetic_diversity_r/RSV_diversity_results_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arimaite/Documents/GitHub/RSV-wastewater-2024-2025/utilities/genetic_diversity/genetic_diversity_r/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40031C54-1EF3-A84F-8282-23CDA9D10807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E617BE-1D68-2842-8489-B55DC41CFB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13520" yWindow="3140" windowWidth="15280" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marginal_means" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,8 +144,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -193,13 +223,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,16 +546,17 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.5" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,326 +582,340 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>3.62E-3</v>
-      </c>
-      <c r="G2">
-        <v>3.0300000000000001E-3</v>
-      </c>
-      <c r="H2">
-        <v>4.3099999999999996E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.3E-3</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2.7200000000000002E-3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>1.7700000000000001E-3</v>
-      </c>
-      <c r="G3">
-        <v>1.4400000000000001E-3</v>
-      </c>
-      <c r="H3">
-        <v>2.16E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1.58E-3</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.25E-3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.98E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>2.4499999999999999E-3</v>
-      </c>
-      <c r="G4">
-        <v>1.67E-3</v>
-      </c>
-      <c r="H4">
-        <v>3.62E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.2399999999999998E-3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.5499999999999999E-3</v>
+      </c>
+      <c r="H4" s="3">
+        <v>3.2299999999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="G5">
-        <v>5.6999999999999998E-4</v>
-      </c>
-      <c r="H5">
-        <v>1.1100000000000001E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7.1000000000000002E-4</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>4.9199999999999999E-3</v>
-      </c>
-      <c r="G6">
-        <v>3.9199999999999999E-3</v>
-      </c>
-      <c r="H6">
-        <v>6.1799999999999997E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.9399999999999999E-3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.0699999999999998E-3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5.0600000000000003E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>4.8799999999999998E-3</v>
-      </c>
-      <c r="G7">
-        <v>3.7699999999999999E-3</v>
-      </c>
-      <c r="H7">
-        <v>6.3299999999999997E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.8600000000000001E-3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.98E-3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>4.9899999999999996E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>2.6700000000000001E-3</v>
-      </c>
-      <c r="G8">
-        <v>1.9599999999999999E-3</v>
-      </c>
-      <c r="H8">
-        <v>3.63E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.1299999999999999E-3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.5900000000000001E-3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.8700000000000002E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>4.7999999999999996E-3</v>
-      </c>
-      <c r="G9">
-        <v>3.8700000000000002E-3</v>
-      </c>
-      <c r="H9">
-        <v>5.96E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.6700000000000001E-3</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.7799999999999999E-3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>4.8399999999999997E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>7.7999999999999999E-4</v>
-      </c>
-      <c r="G10">
-        <v>5.5999999999999995E-4</v>
-      </c>
-      <c r="H10">
-        <v>1.08E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9.7000000000000005E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>4.5399999999999998E-3</v>
-      </c>
-      <c r="G11">
-        <v>3.2699999999999999E-3</v>
-      </c>
-      <c r="H11">
-        <v>6.3099999999999996E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.98E-3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2.8500000000000001E-3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>5.5599999999999998E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F12">
-        <v>15.014570000000001</v>
-      </c>
-      <c r="G12">
-        <v>13.916729999999999</v>
-      </c>
-      <c r="H12">
-        <v>16.199020000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="F12" s="3">
+        <v>14.471360000000001</v>
+      </c>
+      <c r="G12" s="3">
+        <v>13.448600000000001</v>
+      </c>
+      <c r="H12" s="3">
+        <v>15.571899999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F13">
-        <v>38.41339</v>
-      </c>
-      <c r="G13">
-        <v>36.318629999999999</v>
-      </c>
-      <c r="H13">
-        <v>40.628979999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="F13" s="3">
+        <v>37.137169999999998</v>
+      </c>
+      <c r="G13" s="3">
+        <v>34.76182</v>
+      </c>
+      <c r="H13" s="3">
+        <v>39.674840000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F14">
-        <v>12.16433</v>
-      </c>
-      <c r="G14">
-        <v>11.24104</v>
-      </c>
-      <c r="H14">
-        <v>13.16344</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="F14" s="3">
+        <v>11.53857</v>
+      </c>
+      <c r="G14" s="3">
+        <v>10.64608</v>
+      </c>
+      <c r="H14" s="3">
+        <v>12.505879999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F15">
-        <v>32.823839999999997</v>
-      </c>
-      <c r="G15">
-        <v>30.324359999999999</v>
-      </c>
-      <c r="H15">
-        <v>35.529339999999998</v>
+      <c r="F15" s="3">
+        <v>31.092600000000001</v>
+      </c>
+      <c r="G15" s="3">
+        <v>28.54862</v>
+      </c>
+      <c r="H15" s="3">
+        <v>33.86327</v>
       </c>
     </row>
   </sheetData>
@@ -874,257 +927,266 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E2">
-        <v>2.0477408197967648</v>
-      </c>
-      <c r="F2">
-        <v>0.20865111077326129</v>
-      </c>
-      <c r="G2">
-        <v>7.0341917000867911</v>
-      </c>
-      <c r="H2">
-        <v>2.0041942028727439E-12</v>
-      </c>
-      <c r="I2">
-        <v>2.0041942028727439E-12</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="E2" s="4">
+        <v>2.096503639605575</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.21297208468935741</v>
+      </c>
+      <c r="G2" s="4">
+        <v>7.2872503345883084</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3.163447864944428E-13</v>
+      </c>
+      <c r="I2" s="4">
+        <v>3.163447864944428E-13</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E3">
-        <v>3.0772693070939439</v>
-      </c>
-      <c r="F3">
-        <v>0.68392320684195607</v>
-      </c>
-      <c r="G3">
-        <v>5.0575588089332877</v>
-      </c>
-      <c r="H3">
-        <v>4.246574927312364E-7</v>
-      </c>
-      <c r="I3">
-        <v>8.4931498546247279E-7</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="E3" s="4">
+        <v>3.1379126507977082</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.70686635846528512</v>
+      </c>
+      <c r="G3" s="4">
+        <v>5.0764681342837363</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3.845152493999711E-7</v>
+      </c>
+      <c r="I3" s="4">
+        <v>7.6903049879994221E-7</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4">
-        <v>1.007248164337557</v>
-      </c>
-      <c r="F4">
-        <v>0.175160299779692</v>
-      </c>
-      <c r="G4">
-        <v>4.1529781885824318E-2</v>
-      </c>
-      <c r="H4">
-        <v>0.96687355081699644</v>
-      </c>
-      <c r="I4">
-        <v>0.96687355081699644</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="E4" s="4">
+        <v>1.0205723320407469</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.17296510183994551</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.1201543310206062</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.90436089416471821</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.90436089416471821</v>
+      </c>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E5">
-        <v>0.55548767163941926</v>
-      </c>
-      <c r="F5">
-        <v>0.1051317691707024</v>
-      </c>
-      <c r="G5">
-        <v>-3.106350518514343</v>
-      </c>
-      <c r="H5">
-        <v>1.8941204627118749E-3</v>
-      </c>
-      <c r="I5">
-        <v>1.8941204627118749E-3</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="E5" s="4">
+        <v>0.58165255939397942</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.10934052156847809</v>
+      </c>
+      <c r="G5" s="4">
+        <v>-2.882618811536084</v>
+      </c>
+      <c r="H5" s="4">
+        <v>3.9438437466321908E-3</v>
+      </c>
+      <c r="I5" s="4">
+        <v>3.9438437466321908E-3</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E6">
-        <v>0.17128351181869919</v>
-      </c>
-      <c r="F6">
-        <v>3.1529438386845771E-2</v>
-      </c>
-      <c r="G6">
-        <v>-9.585284774092754</v>
-      </c>
-      <c r="H6">
-        <v>9.2202933300534612E-22</v>
-      </c>
-      <c r="I6">
-        <v>1.229372444007128E-21</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="E6" s="4">
+        <v>0.17647079805618959</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3.2657919874596521E-2</v>
+      </c>
+      <c r="G6" s="4">
+        <v>-9.3731083886496158</v>
+      </c>
+      <c r="H6" s="4">
+        <v>7.0427242897070972E-21</v>
+      </c>
+      <c r="I6" s="4">
+        <v>9.3902990529427957E-21</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E7">
-        <v>0.3908681535417583</v>
-      </c>
-      <c r="F7">
-        <v>1.815633275743915E-2</v>
-      </c>
-      <c r="G7">
-        <v>-20.223008530598971</v>
-      </c>
-      <c r="H7">
-        <v>6.1420815926274584E-91</v>
-      </c>
-      <c r="I7">
-        <v>1.2284163185254919E-90</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="E7" s="4">
+        <v>0.38967328435406079</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1.8207090125580319E-2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>-20.170508770320581</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.7780022913397489E-90</v>
+      </c>
+      <c r="I7" s="4">
+        <v>3.5560045826794991E-90</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E8">
-        <v>0.37059429412587808</v>
-      </c>
-      <c r="F8">
-        <v>1.7641988845173869E-2</v>
-      </c>
-      <c r="G8">
-        <v>-20.851926135033921</v>
-      </c>
-      <c r="H8">
-        <v>1.464088204726372E-96</v>
-      </c>
-      <c r="I8">
-        <v>5.8563528189054862E-96</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="E8" s="4">
+        <v>0.37110335614222251</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1.7881135260941271E-2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>-20.572818810673621</v>
+      </c>
+      <c r="H8" s="4">
+        <v>4.808815646500384E-94</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.923526258600154E-93</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>32</v>
       </c>
     </row>

--- a/utilities/genetic_diversity/genetic_diversity_r/RSV_diversity_results_final.xlsx
+++ b/utilities/genetic_diversity/genetic_diversity_r/RSV_diversity_results_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arimaite/Documents/GitHub/RSV-wastewater-2024-2025/utilities/genetic_diversity/genetic_diversity_r/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E617BE-1D68-2842-8489-B55DC41CFB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7422070B-87C3-4342-AAD1-9F8AE75BD53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marginal_means" sheetId="1" r:id="rId1"/>
@@ -231,14 +231,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,338 +583,338 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6">
         <v>3.3E-3</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="6">
         <v>2.7200000000000002E-3</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="6">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6">
         <v>1.58E-3</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="6">
         <v>1.25E-3</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="6">
         <v>1.98E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6">
         <v>2.2399999999999998E-3</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="6">
         <v>1.5499999999999999E-3</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="6">
         <v>3.2299999999999998E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6">
         <v>7.1000000000000002E-4</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="6">
         <v>5.1000000000000004E-4</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="6">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="6">
         <v>3.9399999999999999E-3</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="6">
         <v>3.0699999999999998E-3</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="6">
         <v>5.0600000000000003E-3</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6">
         <v>3.8600000000000001E-3</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="6">
         <v>2.98E-3</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="6">
         <v>4.9899999999999996E-3</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6">
         <v>2.1299999999999999E-3</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="6">
         <v>1.5900000000000001E-3</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="6">
         <v>2.8700000000000002E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6">
         <v>3.6700000000000001E-3</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="6">
         <v>2.7799999999999999E-3</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="6">
         <v>4.8399999999999997E-3</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="6">
         <v>5.1000000000000004E-4</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="6">
         <v>9.7000000000000005E-4</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="E11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6">
         <v>3.98E-3</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="6">
         <v>2.8500000000000001E-3</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="6">
         <v>5.5599999999999998E-3</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="6">
         <v>14.471360000000001</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="6">
         <v>13.448600000000001</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="6">
         <v>15.571899999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="6">
         <v>37.137169999999998</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="6">
         <v>34.76182</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="6">
         <v>39.674840000000003</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="6">
         <v>11.53857</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="6">
         <v>10.64608</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="6">
         <v>12.505879999999999</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="6">
         <v>31.092600000000001</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="6">
         <v>28.54862</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="6">
         <v>33.86327</v>
       </c>
     </row>
@@ -937,34 +937,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
